--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1fa7e4f6244850e5/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE435810-F467-4C33-8754-B050B8BE575B}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>Project Title</t>
-  </si>
-  <si>
-    <t>&lt;&lt;e.g. AITA-mini: Assignment Submission &amp; Grading Portal&gt;&gt;</t>
   </si>
   <si>
     <t>List of Student</t>
@@ -282,6 +279,9 @@
   </si>
   <si>
     <t>QE200042</t>
+  </si>
+  <si>
+    <t>AITA-mini: Assignment Submission &amp; Grading Portal</t>
   </si>
 </sst>
 </file>
@@ -292,7 +292,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -301,27 +301,32 @@
       <sz val="14"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="6">
@@ -436,21 +441,21 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -751,14 +756,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="11"/>
@@ -766,184 +771,188 @@
       <c r="D1" s="11"/>
       <c r="E1" s="11"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="12" t="s">
         <v>2</v>
       </c>
       <c r="C3" s="11"/>
       <c r="D3" s="11"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="12" t="s">
         <v>4</v>
       </c>
       <c r="C4" s="11"/>
       <c r="D4" s="11"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>71</v>
+      <c r="B5" s="12" t="s">
+        <v>70</v>
       </c>
       <c r="C5" s="11"/>
       <c r="D5" s="11"/>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>70</v>
+      <c r="B6" s="12" t="s">
+        <v>69</v>
       </c>
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="10"/>
+      <c r="B7" s="12" t="s">
+        <v>76</v>
+      </c>
       <c r="C7" s="11"/>
       <c r="D7" s="11"/>
       <c r="E7" s="11"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>72</v>
+      <c r="B8" s="12" t="s">
+        <v>71</v>
       </c>
       <c r="C8" s="11"/>
       <c r="D8" s="11"/>
       <c r="E8" s="11"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>10</v>
+      <c r="B9" s="12" t="s">
+        <v>84</v>
       </c>
       <c r="C9" s="11"/>
       <c r="D9" s="11"/>
       <c r="E9" s="11"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" s="14"/>
+      <c r="C11" s="14"/>
+      <c r="D11" s="14"/>
+      <c r="E11" s="15"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E17" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="B7:E7"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="B5:E5"/>
@@ -951,8 +960,6 @@
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B4:E4"/>
     <mergeCell ref="B6:E6"/>
-    <mergeCell ref="A11:E11"/>
-    <mergeCell ref="B7:E7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -961,7 +968,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -975,100 +982,100 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>32</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>33</v>
       </c>
       <c r="I2" s="5">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>40</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>41</v>
       </c>
       <c r="I3" s="5">
         <v>4</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -1079,7 +1086,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1093,100 +1100,100 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="C1" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="J1" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="J1" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="F2" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="H2" s="6" t="s">
         <v>48</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>49</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D3" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="H3" s="6" t="s">
         <v>55</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>56</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
@@ -1197,98 +1204,98 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="7" t="s">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="9" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" s="8" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B3" s="9" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="8" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="9" t="s">
+      <c r="B4" s="9" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="8" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B5" s="9" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" s="8" t="s">
+    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B6" s="9" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="B7" s="9" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="8" t="s">
+    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B8" s="9" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="8" t="s">
+    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="B9" s="9" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="8" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B10" s="9" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" s="8" t="s">
+    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A11" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B11" s="9" t="s">
         <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE435810-F467-4C33-8754-B050B8BE575B}"/>
+  <xr:revisionPtr revIDLastSave="40" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9B9EA82-D4D9-4025-AE89-D3D1005130F4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="86">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -282,6 +282,9 @@
   </si>
   <si>
     <t>AITA-mini: Assignment Submission &amp; Grading Portal</t>
+  </si>
+  <si>
+    <t>ERD Design for AITA System (User, Course, Submission tables)</t>
   </si>
 </sst>
 </file>
@@ -361,7 +364,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -408,11 +411,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -441,18 +453,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
@@ -468,6 +482,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -763,99 +781,99 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
+      <c r="B1" s="14"/>
+      <c r="C1" s="14"/>
+      <c r="D1" s="14"/>
+      <c r="E1" s="14"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="11"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
+      <c r="C4" s="14"/>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="12" t="s">
+      <c r="B5" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="11"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="13" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
+      <c r="C6" s="14"/>
+      <c r="D6" s="14"/>
+      <c r="E6" s="14"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="12" t="s">
+      <c r="B7" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
+      <c r="C7" s="14"/>
+      <c r="D7" s="14"/>
+      <c r="E7" s="14"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="12" t="s">
+      <c r="B8" s="13" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="11"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="11"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="12" t="s">
+      <c r="B9" s="13" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="11"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="11"/>
+      <c r="C9" s="14"/>
+      <c r="D9" s="14"/>
+      <c r="E9" s="14"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="14"/>
-      <c r="C11" s="14"/>
-      <c r="D11" s="14"/>
-      <c r="E11" s="15"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
@@ -967,7 +985,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
@@ -1077,6 +1095,334 @@
       <c r="J3" s="6" t="s">
         <v>41</v>
       </c>
+    </row>
+    <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>3</v>
+      </c>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="6"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A5" s="5"/>
+      <c r="B5" s="6"/>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="6"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="5"/>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="6"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="5"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="5"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6"/>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="6"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="5"/>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="5"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="6"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="6"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="5"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="6"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="6"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="5"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+      <c r="G12" s="6"/>
+      <c r="H12" s="6"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="5"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="5"/>
+      <c r="B14" s="6"/>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="6"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="5"/>
+      <c r="B15" s="6"/>
+      <c r="C15" s="6"/>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="5"/>
+      <c r="B16" s="6"/>
+      <c r="C16" s="6"/>
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="6"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="16"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="16"/>
+      <c r="D17" s="16"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="16"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="16"/>
+      <c r="J17" s="16"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="16"/>
+      <c r="B18" s="16"/>
+      <c r="C18" s="16"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="16"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16"/>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="16"/>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="16"/>
+      <c r="B20" s="16"/>
+      <c r="C20" s="16"/>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16"/>
+      <c r="F20" s="16"/>
+      <c r="G20" s="16"/>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16"/>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="16"/>
+      <c r="B21" s="16"/>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="16"/>
+      <c r="I21" s="16"/>
+      <c r="J21" s="16"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="16"/>
+      <c r="B22" s="16"/>
+      <c r="C22" s="16"/>
+      <c r="D22" s="16"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="16"/>
+      <c r="G22" s="16"/>
+      <c r="H22" s="16"/>
+      <c r="I22" s="16"/>
+      <c r="J22" s="16"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="16"/>
+      <c r="B23" s="16"/>
+      <c r="C23" s="16"/>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="F23" s="16"/>
+      <c r="G23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
+      <c r="J23" s="16"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="16"/>
+      <c r="B24" s="16"/>
+      <c r="C24" s="16"/>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16"/>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16"/>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16"/>
+      <c r="J24" s="16"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="16"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="16"/>
+      <c r="D25" s="16"/>
+      <c r="E25" s="16"/>
+      <c r="F25" s="16"/>
+      <c r="G25" s="16"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="16"/>
+      <c r="J25" s="16"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="16"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16"/>
+      <c r="J26" s="16"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
+      <c r="G27" s="16"/>
+      <c r="H27" s="16"/>
+      <c r="I27" s="16"/>
+      <c r="J27" s="16"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="16"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
+      <c r="D28" s="16"/>
+      <c r="E28" s="16"/>
+      <c r="F28" s="16"/>
+      <c r="G28" s="16"/>
+      <c r="H28" s="16"/>
+      <c r="I28" s="16"/>
+      <c r="J28" s="16"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="16"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16"/>
+      <c r="J29" s="16"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="17"/>
+      <c r="B30" s="17"/>
+      <c r="C30" s="17"/>
+      <c r="D30" s="17"/>
+      <c r="E30" s="17"/>
+      <c r="F30" s="17"/>
+      <c r="G30" s="17"/>
+      <c r="H30" s="17"/>
+      <c r="I30" s="17"/>
+      <c r="J30" s="17"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B9B9EA82-D4D9-4025-AE89-D3D1005130F4}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EBCA9E4-CF6A-4C54-8BE4-2D3796176E08}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -285,6 +285,21 @@
   </si>
   <si>
     <t>ERD Design for AITA System (User, Course, Submission tables)</t>
+  </si>
+  <si>
+    <t>Suggested 6 core tables with primary keys and relationships (Users, Roles, Courses, Submissions, AILogs, Rubrics)</t>
+  </si>
+  <si>
+    <t>Adjusted foreign keys, added SHA-256 hash column for Submissions table, normalized to 3NF</t>
+  </si>
+  <si>
+    <t>Link Google Drive chứa ảnh chụp màn hình chat (Đặt tên ảnh: GroupX_Session1_ERD.png)</t>
+  </si>
+  <si>
+    <t>6 tables, 8 foreign key relationships</t>
+  </si>
+  <si>
+    <t>Missing composite index for fast querying, initial schema was not fully optimized for JDBC DAO pattern</t>
   </si>
 </sst>
 </file>
@@ -1096,21 +1111,37 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="B4" s="6"/>
+      <c r="B4" s="6" t="s">
+        <v>34</v>
+      </c>
       <c r="C4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="6"/>
+      <c r="D4" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="5">
+        <v>4</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\LABnhom6\PRJ301-Nh-m-6\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="8_{6A6AFAC0-BF14-49DE-A319-EA4C234F04ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EBCA9E4-CF6A-4C54-8BE4-2D3796176E08}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -293,24 +292,45 @@
     <t>Adjusted foreign keys, added SHA-256 hash column for Submissions table, normalized to 3NF</t>
   </si>
   <si>
-    <t>Link Google Drive chứa ảnh chụp màn hình chat (Đặt tên ảnh: GroupX_Session1_ERD.png)</t>
-  </si>
-  <si>
     <t>6 tables, 8 foreign key relationships</t>
   </si>
   <si>
     <t>Missing composite index for fast querying, initial schema was not fully optimized for JDBC DAO pattern</t>
+  </si>
+  <si>
+    <t>UI/UX Prototype drafting for Lecturer &amp; Student Dashboard</t>
+  </si>
+  <si>
+    <t>GroupX_Session1_ERD.png</t>
+  </si>
+  <si>
+    <t>Claue</t>
+  </si>
+  <si>
+    <t>HTML/CSS wireframe outline for student submission portal and lecturer grading panel</t>
+  </si>
+  <si>
+    <t>Customized CSS layout to fit FPT University theme, added file upload interface for ZIP/SHA-256 artifacts</t>
+  </si>
+  <si>
+    <t>GroupX_Session1_UI</t>
+  </si>
+  <si>
+    <t>2 HTML/CSS layout templates</t>
+  </si>
+  <si>
+    <t>Generated layout was too generic, lacked responsive design for mobile views</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -468,6 +488,8 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -480,11 +502,9 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -787,110 +807,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="14"/>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="15" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="14"/>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="14"/>
-      <c r="D7" s="14"/>
-      <c r="E7" s="14"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="14"/>
-      <c r="D8" s="14"/>
-      <c r="E8" s="14"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="14"/>
-      <c r="D9" s="14"/>
-      <c r="E9" s="14"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="11"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="12"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="14"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -907,7 +927,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -922,7 +942,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -937,7 +957,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -952,7 +972,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -967,7 +987,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -999,9 +1019,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1015,7 +1035,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1047,7 +1067,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1079,7 +1099,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1111,7 +1131,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1131,31 +1151,51 @@
         <v>87</v>
       </c>
       <c r="G4" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>88</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>89</v>
       </c>
       <c r="I4" s="5">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5"/>
-      <c r="B5" s="6"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="6"/>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="D5" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" s="5">
+        <v>4</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="5"/>
       <c r="B6" s="6"/>
       <c r="C6" s="6"/>
@@ -1167,7 +1207,7 @@
       <c r="I6" s="5"/>
       <c r="J6" s="6"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1179,7 +1219,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1191,7 +1231,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1203,7 +1243,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1215,7 +1255,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1227,7 +1267,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1239,7 +1279,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1251,7 +1291,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1263,7 +1303,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1275,7 +1315,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1287,173 +1327,173 @@
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="16"/>
-      <c r="B17" s="16"/>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
-      <c r="I17" s="16"/>
-      <c r="J17" s="16"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" s="16"/>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" s="16"/>
-      <c r="B19" s="16"/>
-      <c r="C19" s="16"/>
-      <c r="D19" s="16"/>
-      <c r="E19" s="16"/>
-      <c r="F19" s="16"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="16"/>
-      <c r="I19" s="16"/>
-      <c r="J19" s="16"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" s="16"/>
-      <c r="B20" s="16"/>
-      <c r="C20" s="16"/>
-      <c r="D20" s="16"/>
-      <c r="E20" s="16"/>
-      <c r="F20" s="16"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="16"/>
-      <c r="I20" s="16"/>
-      <c r="J20" s="16"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" s="16"/>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="16"/>
-      <c r="J21" s="16"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" s="16"/>
-      <c r="B22" s="16"/>
-      <c r="C22" s="16"/>
-      <c r="D22" s="16"/>
-      <c r="E22" s="16"/>
-      <c r="F22" s="16"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="16"/>
-      <c r="I22" s="16"/>
-      <c r="J22" s="16"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" s="16"/>
-      <c r="B23" s="16"/>
-      <c r="C23" s="16"/>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="16"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
-      <c r="J23" s="16"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" s="16"/>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
-      <c r="H24" s="16"/>
-      <c r="I24" s="16"/>
-      <c r="J24" s="16"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" s="16"/>
-      <c r="B25" s="16"/>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="16"/>
-      <c r="F25" s="16"/>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="16"/>
-      <c r="J25" s="16"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" s="16"/>
-      <c r="B26" s="16"/>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16"/>
-      <c r="J26" s="16"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" s="16"/>
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
-      <c r="G27" s="16"/>
-      <c r="H27" s="16"/>
-      <c r="I27" s="16"/>
-      <c r="J27" s="16"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" s="16"/>
-      <c r="B28" s="16"/>
-      <c r="C28" s="16"/>
-      <c r="D28" s="16"/>
-      <c r="E28" s="16"/>
-      <c r="F28" s="16"/>
-      <c r="G28" s="16"/>
-      <c r="H28" s="16"/>
-      <c r="I28" s="16"/>
-      <c r="J28" s="16"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" s="16"/>
-      <c r="B29" s="16"/>
-      <c r="C29" s="16"/>
-      <c r="D29" s="16"/>
-      <c r="E29" s="16"/>
-      <c r="F29" s="16"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="16"/>
-      <c r="I29" s="16"/>
-      <c r="J29" s="16"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="17"/>
-      <c r="G30" s="17"/>
-      <c r="H30" s="17"/>
-      <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A17" s="10"/>
+      <c r="B17" s="10"/>
+      <c r="C17" s="10"/>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10"/>
+      <c r="J17" s="10"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A18" s="10"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10"/>
+      <c r="J18" s="10"/>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A19" s="10"/>
+      <c r="B19" s="10"/>
+      <c r="C19" s="10"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10"/>
+      <c r="J19" s="10"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A20" s="10"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10"/>
+      <c r="J20" s="10"/>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A21" s="10"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A22" s="10"/>
+      <c r="B22" s="10"/>
+      <c r="C22" s="10"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10"/>
+      <c r="J22" s="10"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A23" s="10"/>
+      <c r="B23" s="10"/>
+      <c r="C23" s="10"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10"/>
+      <c r="J23" s="10"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A24" s="10"/>
+      <c r="B24" s="10"/>
+      <c r="C24" s="10"/>
+      <c r="D24" s="10"/>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10"/>
+      <c r="J24" s="10"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A25" s="10"/>
+      <c r="B25" s="10"/>
+      <c r="C25" s="10"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10"/>
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A26" s="10"/>
+      <c r="B26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10"/>
+      <c r="J26" s="10"/>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A27" s="10"/>
+      <c r="B27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="10"/>
+      <c r="E27" s="10"/>
+      <c r="F27" s="10"/>
+      <c r="G27" s="10"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
+      <c r="J27" s="10"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A28" s="10"/>
+      <c r="B28" s="10"/>
+      <c r="C28" s="10"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10"/>
+      <c r="F28" s="10"/>
+      <c r="G28" s="10"/>
+      <c r="H28" s="10"/>
+      <c r="I28" s="10"/>
+      <c r="J28" s="10"/>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A29" s="10"/>
+      <c r="B29" s="10"/>
+      <c r="C29" s="10"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10"/>
+      <c r="F29" s="10"/>
+      <c r="G29" s="10"/>
+      <c r="H29" s="10"/>
+      <c r="I29" s="10"/>
+      <c r="J29" s="10"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="11"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1461,9 +1501,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1477,7 +1517,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1509,7 +1549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1541,7 +1581,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1579,15 +1619,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
@@ -1595,7 +1635,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>16</v>
       </c>
@@ -1603,7 +1643,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
@@ -1611,7 +1651,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
@@ -1619,7 +1659,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
@@ -1627,7 +1667,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
@@ -1635,7 +1675,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -1643,7 +1683,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -1651,7 +1691,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
@@ -1659,7 +1699,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>24</v>
       </c>
@@ -1667,7 +1707,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>25</v>
       </c>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\LABnhom6\PRJ301-Nh-m-6\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5E2EF33-0CC3-4E8D-86B2-19392B8DCED5}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -320,17 +321,39 @@
   </si>
   <si>
     <t>Generated layout was too generic, lacked responsive design for mobile views</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	
+Requirement</t>
+  </si>
+  <si>
+    <t>Research JDBC Advanced setup &amp; DAO pattern connection structure</t>
+  </si>
+  <si>
+    <t>Sample DBContext class template with Connection Pooling / JDBC driver configuration</t>
+  </si>
+  <si>
+    <t>Replaced credentials with local SQL Server context, wrapped connection with try-with-resources</t>
+  </si>
+  <si>
+    <t>GroupX_Session1_JDBC.png</t>
+  </si>
+  <si>
+    <t>1 DBContext Java class, ~35 LOC</t>
+  </si>
+  <si>
+    <t>Hardcoded database passwords in output code without environment variable separation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -459,7 +482,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -488,7 +511,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -504,7 +526,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -517,10 +539,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -807,110 +825,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B1" s="15"/>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C6" s="15"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="15"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C7" s="15"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="15"/>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="C8" s="15"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
+      <c r="C9" s="15"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="15"/>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="14"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="13"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -927,7 +945,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -942,7 +960,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -957,7 +975,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -972,7 +990,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -987,7 +1005,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -1019,9 +1037,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1035,7 +1053,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1067,7 +1085,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1099,7 +1117,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1131,7 +1149,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1163,7 +1181,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1195,19 +1213,39 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A6" s="5"/>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="6"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="6"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" s="5">
+        <v>5</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1219,7 +1257,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1231,7 +1269,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1243,7 +1281,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1255,7 +1293,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1267,7 +1305,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1279,7 +1317,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1291,7 +1329,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1303,7 +1341,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1315,7 +1353,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1327,173 +1365,17 @@
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="10"/>
-      <c r="B17" s="10"/>
-      <c r="C17" s="10"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
-      <c r="H17" s="10"/>
-      <c r="I17" s="10"/>
-      <c r="J17" s="10"/>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="10"/>
-      <c r="B18" s="10"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="10"/>
-      <c r="I18" s="10"/>
-      <c r="J18" s="10"/>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="10"/>
-      <c r="B19" s="10"/>
-      <c r="C19" s="10"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
-      <c r="H19" s="10"/>
-      <c r="I19" s="10"/>
-      <c r="J19" s="10"/>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="10"/>
-      <c r="B20" s="10"/>
-      <c r="C20" s="10"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
-      <c r="H20" s="10"/>
-      <c r="I20" s="10"/>
-      <c r="J20" s="10"/>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="10"/>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="10"/>
-      <c r="B22" s="10"/>
-      <c r="C22" s="10"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
-      <c r="H22" s="10"/>
-      <c r="I22" s="10"/>
-      <c r="J22" s="10"/>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="10"/>
-      <c r="B23" s="10"/>
-      <c r="C23" s="10"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
-      <c r="H23" s="10"/>
-      <c r="I23" s="10"/>
-      <c r="J23" s="10"/>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="10"/>
-      <c r="B24" s="10"/>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="10"/>
-      <c r="B25" s="10"/>
-      <c r="C25" s="10"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
-      <c r="H25" s="10"/>
-      <c r="I25" s="10"/>
-      <c r="J25" s="10"/>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="10"/>
-      <c r="B26" s="10"/>
-      <c r="C26" s="10"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
-      <c r="H26" s="10"/>
-      <c r="I26" s="10"/>
-      <c r="J26" s="10"/>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="10"/>
-      <c r="B27" s="10"/>
-      <c r="C27" s="10"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="10"/>
-      <c r="F27" s="10"/>
-      <c r="G27" s="10"/>
-      <c r="H27" s="10"/>
-      <c r="I27" s="10"/>
-      <c r="J27" s="10"/>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="10"/>
-      <c r="B28" s="10"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="10"/>
-      <c r="F28" s="10"/>
-      <c r="G28" s="10"/>
-      <c r="H28" s="10"/>
-      <c r="I28" s="10"/>
-      <c r="J28" s="10"/>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="10"/>
-      <c r="B29" s="10"/>
-      <c r="C29" s="10"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="10"/>
-      <c r="F29" s="10"/>
-      <c r="G29" s="10"/>
-      <c r="H29" s="10"/>
-      <c r="I29" s="10"/>
-      <c r="J29" s="10"/>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11"/>
-      <c r="F30" s="11"/>
-      <c r="G30" s="11"/>
-      <c r="H30" s="11"/>
-      <c r="I30" s="11"/>
-      <c r="J30" s="11"/>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="10"/>
+      <c r="B30" s="10"/>
+      <c r="C30" s="10"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10"/>
+      <c r="F30" s="10"/>
+      <c r="G30" s="10"/>
+      <c r="H30" s="10"/>
+      <c r="I30" s="10"/>
+      <c r="J30" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1501,9 +1383,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1517,7 +1399,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1549,7 +1431,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1581,7 +1463,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1619,15 +1501,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
@@ -1635,7 +1517,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>16</v>
       </c>
@@ -1643,7 +1525,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
@@ -1651,7 +1533,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
@@ -1659,7 +1541,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
@@ -1667,7 +1549,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
@@ -1675,7 +1557,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -1683,7 +1565,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -1691,7 +1573,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
@@ -1699,7 +1581,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>24</v>
       </c>
@@ -1707,7 +1589,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>25</v>
       </c>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1fa7e4f6244850e5/Documents/Pictures/Nhom6_Prj/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5E2EF33-0CC3-4E8D-86B2-19392B8DCED5}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{13A3B934-FAA7-42B9-8102-9269B5938F25}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="4596" yWindow="3360" windowWidth="17280" windowHeight="8880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="106">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -343,6 +343,9 @@
   </si>
   <si>
     <t>Hardcoded database passwords in output code without environment variable separation</t>
+  </si>
+  <si>
+    <t>Chat GPT, Gemini, Claude</t>
   </si>
 </sst>
 </file>
@@ -353,7 +356,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -526,7 +529,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -827,13 +830,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -842,7 +845,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -853,7 +856,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -864,7 +867,7 @@
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -875,7 +878,7 @@
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -886,7 +889,7 @@
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -897,7 +900,7 @@
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -908,7 +911,7 @@
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -919,7 +922,7 @@
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
@@ -928,7 +931,7 @@
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -945,7 +948,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -958,9 +961,11 @@
       <c r="D13" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="E13" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -975,7 +980,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -990,7 +995,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -1005,7 +1010,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -1039,7 +1044,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1053,7 +1058,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1085,7 +1090,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1117,7 +1122,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1149,7 +1154,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="66" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1181,7 +1186,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1213,7 +1218,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1245,7 +1250,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="5"/>
       <c r="B7" s="6"/>
       <c r="C7" s="6"/>
@@ -1257,7 +1262,7 @@
       <c r="I7" s="5"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="5"/>
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
@@ -1269,7 +1274,7 @@
       <c r="I8" s="5"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="5"/>
       <c r="B9" s="6"/>
       <c r="C9" s="6"/>
@@ -1281,7 +1286,7 @@
       <c r="I9" s="5"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="5"/>
       <c r="B10" s="6"/>
       <c r="C10" s="6"/>
@@ -1293,7 +1298,7 @@
       <c r="I10" s="5"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="5"/>
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
@@ -1305,7 +1310,7 @@
       <c r="I11" s="5"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1317,7 +1322,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1329,7 +1334,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1341,7 +1346,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1353,7 +1358,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1365,7 +1370,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -1385,7 +1390,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1399,7 +1404,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1431,7 +1436,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1463,7 +1468,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1503,13 +1508,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>57</v>
       </c>
@@ -1517,7 +1522,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>16</v>
       </c>
@@ -1525,7 +1530,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
@@ -1533,7 +1538,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
@@ -1541,7 +1546,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
@@ -1549,7 +1554,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
@@ -1557,7 +1562,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -1565,7 +1570,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -1573,7 +1578,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
@@ -1581,7 +1586,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>24</v>
       </c>
@@ -1589,7 +1594,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>25</v>
       </c>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5E2EF33-0CC3-4E8D-86B2-19392B8DCED5}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271C5304-3FA0-4FF8-8C58-0751B1D05874}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -103,53 +103,10 @@
     <t>Risks / Limitations Observed</t>
   </si>
   <si>
-    <t>&lt;&lt;sample data&gt;&gt;
-Requirement</t>
-  </si>
-  <si>
-    <t>Use Case &amp; SRS drafting (Servlet/JSP scope)</t>
-  </si>
-  <si>
     <t>ChatGPT</t>
   </si>
   <si>
-    <t>8 use cases + draft SRS outline</t>
-  </si>
-  <si>
-    <t>Kept 6 use cases, merged 2 duplicates, rewrote acceptance criteria</t>
-  </si>
-  <si>
-    <t>Google Doc link</t>
-  </si>
-  <si>
-    <t>6 use cases kept</t>
-  </si>
-  <si>
-    <t>Some use cases too generic, not FPT-specific</t>
-  </si>
-  <si>
     <t>Design</t>
-  </si>
-  <si>
-    <t>ERD for Submission/Grading module (reference: AITA Submission &amp; Rubric tables)</t>
-  </si>
-  <si>
-    <t>Copilot</t>
-  </si>
-  <si>
-    <t>Suggested 5 tables (User, Class, Assignment, Submission, Score)</t>
-  </si>
-  <si>
-    <t>Adjusted PK/FK, added AttemptNumber column, normalized to 3NF</t>
-  </si>
-  <si>
-    <t>draw.io link</t>
-  </si>
-  <si>
-    <t>5 entities, 6 relationships</t>
-  </si>
-  <si>
-    <t>Missing cascade delete rules</t>
   </si>
   <si>
     <t>&lt;&lt;sample data&gt;&gt;
@@ -284,65 +241,100 @@
     <t>AITA-mini: Assignment Submission &amp; Grading Portal</t>
   </si>
   <si>
-    <t>ERD Design for AITA System (User, Course, Submission tables)</t>
-  </si>
-  <si>
-    <t>Suggested 6 core tables with primary keys and relationships (Users, Roles, Courses, Submissions, AILogs, Rubrics)</t>
-  </si>
-  <si>
-    <t>Adjusted foreign keys, added SHA-256 hash column for Submissions table, normalized to 3NF</t>
-  </si>
-  <si>
-    <t>6 tables, 8 foreign key relationships</t>
-  </si>
-  <si>
-    <t>Missing composite index for fast querying, initial schema was not fully optimized for JDBC DAO pattern</t>
-  </si>
-  <si>
-    <t>UI/UX Prototype drafting for Lecturer &amp; Student Dashboard</t>
-  </si>
-  <si>
-    <t>GroupX_Session1_ERD.png</t>
-  </si>
-  <si>
-    <t>Claue</t>
-  </si>
-  <si>
-    <t>HTML/CSS wireframe outline for student submission portal and lecturer grading panel</t>
-  </si>
-  <si>
-    <t>Customized CSS layout to fit FPT University theme, added file upload interface for ZIP/SHA-256 artifacts</t>
-  </si>
-  <si>
-    <t>GroupX_Session1_UI</t>
-  </si>
-  <si>
-    <t>2 HTML/CSS layout templates</t>
-  </si>
-  <si>
-    <t>Generated layout was too generic, lacked responsive design for mobile views</t>
-  </si>
-  <si>
-    <t xml:space="preserve">	
-Requirement</t>
-  </si>
-  <si>
-    <t>Research JDBC Advanced setup &amp; DAO pattern connection structure</t>
-  </si>
-  <si>
-    <t>Sample DBContext class template with Connection Pooling / JDBC driver configuration</t>
-  </si>
-  <si>
-    <t>Replaced credentials with local SQL Server context, wrapped connection with try-with-resources</t>
-  </si>
-  <si>
-    <t>GroupX_Session1_JDBC.png</t>
-  </si>
-  <si>
-    <t>1 DBContext Java class, ~35 LOC</t>
-  </si>
-  <si>
-    <t>Hardcoded database passwords in output code without environment variable separation</t>
+    <t>ERD Design for Git Analytics module (GitCommits, GitAuthors, ContributionScores)</t>
+  </si>
+  <si>
+    <t>Suggested 3 tables (git_commits, git_metrics, user_contributions) with PK/FK definitions.</t>
+  </si>
+  <si>
+    <t>Added lines_added and lines_deleted columns to measure code volume, linked author_email to Users table.</t>
+  </si>
+  <si>
+    <t>3 tables, 4 foreign key relationships</t>
+  </si>
+  <si>
+    <t>AI schema initially lacked indexing on commit_date, which could slow down historical query performance.</t>
+  </si>
+  <si>
+    <t>Requirement</t>
+  </si>
+  <si>
+    <t>Research Git analytics metrics and logic to assess individual contribution and detect free-riding</t>
+  </si>
+  <si>
+    <t>Gemini</t>
+  </si>
+  <si>
+    <t>Suggested contribution formula based on weighted sum of Commits, LOC, and Active Days.</t>
+  </si>
+  <si>
+    <t>Adjusted weights: reduced raw LOC weight to prevent spamming code, increased commit frequency weight.</t>
+  </si>
+  <si>
+    <t>1 contribution scoring algorithm outline</t>
+  </si>
+  <si>
+    <t>Formula might unfairly penalize members working on UI/UX or documentation rather than Java code.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI/UX Prototype drafting for Git Teamwork Assessor Dashboard (Lecturer view)  </t>
+  </si>
+  <si>
+    <t>HTML/CSS layout structure for displaying team contribution pie-charts and free-riding warning alerts.</t>
+  </si>
+  <si>
+    <t>Customized CSS colors to flag low-contribution members in red (&lt; 10%).</t>
+  </si>
+  <si>
+    <t>1 HTML/CSS dashboard template</t>
+  </si>
+  <si>
+    <t>Generated layout used static dummy data and lacked responsive chart integration (Chart.js required later).</t>
+  </si>
+  <si>
+    <t>esearch GitHub REST API endpoints (/repos/{owner}/{repo}/commits) for fetching team commit logs</t>
+  </si>
+  <si>
+    <t>Detailed JSON payload structure and sample HTTP Request headers for GitHub API authentication using Personal Access Token (PAT).</t>
+  </si>
+  <si>
+    <t>Configured rate-limiting strategies and decided to store PAT in environment variables rather than hardcoding in Java.</t>
+  </si>
+  <si>
+    <t>1 API Integration guide, 3 API endpoints identified</t>
+  </si>
+  <si>
+    <t>GitHub API limits unauthenticated requests to 60/hour; requires OAuth/PAT setup for production.</t>
+  </si>
+  <si>
+    <t>Generate SQL DDL scripts to create tables for Git Analytics module (tbl_git_commits, tbl_team_metrics)</t>
+  </si>
+  <si>
+    <t>Executable SQL Server CREATE TABLE statements with primary keys, foreign keys, and indexes on commit_sha and author_email.</t>
+  </si>
+  <si>
+    <t>Modified data types (NVARCHAR(MAX) for commit messages, DATETIME2 for commit timestamps) and added composite index for group ID and date range.</t>
+  </si>
+  <si>
+    <t>1 SQL DDL file, 3 tables, ~80 LOC</t>
+  </si>
+  <si>
+    <t>Initial SQL script used MySQL syntax (AUTO_INCREMENT) instead of SQL Server IDENTITY.</t>
+  </si>
+  <si>
+    <t>Group6_Session1_GitERD.png</t>
+  </si>
+  <si>
+    <t>Group6_Session1_Metrics.png</t>
+  </si>
+  <si>
+    <t>Group6_Session1_GitUI.png</t>
+  </si>
+  <si>
+    <t>Group6_Session1_GitHubAPI.png</t>
+  </si>
+  <si>
+    <t>Group6_Session1_GitDDL.png</t>
   </si>
 </sst>
 </file>
@@ -869,7 +861,7 @@
         <v>5</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
@@ -880,7 +872,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="14" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="C6" s="15"/>
       <c r="D6" s="15"/>
@@ -890,9 +882,7 @@
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="14" t="s">
-        <v>76</v>
-      </c>
+      <c r="B7" s="14"/>
       <c r="C7" s="15"/>
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
@@ -902,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="14" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="C8" s="15"/>
       <c r="D8" s="15"/>
@@ -913,7 +903,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>84</v>
+        <v>70</v>
       </c>
       <c r="C9" s="15"/>
       <c r="D9" s="15"/>
@@ -950,13 +940,13 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E13" s="2"/>
     </row>
@@ -965,13 +955,13 @@
         <v>2</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E14" s="2"/>
     </row>
@@ -980,13 +970,13 @@
         <v>3</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2"/>
     </row>
@@ -995,13 +985,13 @@
         <v>4</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="E16" s="2"/>
     </row>
@@ -1010,13 +1000,13 @@
         <v>5</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>83</v>
+        <v>69</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2"/>
     </row>
@@ -1085,68 +1075,68 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D2" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>28</v>
-      </c>
       <c r="E2" s="6" t="s">
-        <v>29</v>
+        <v>72</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>31</v>
+        <v>98</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="I2" s="5">
         <v>4</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>35</v>
+        <v>77</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>38</v>
+        <v>80</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="I3" s="5">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>41</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
@@ -1154,95 +1144,95 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="F4" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="G4" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>86</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>88</v>
       </c>
       <c r="I4" s="5">
         <v>4</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>76</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F5" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="G5" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="I5" s="5">
+        <v>5</v>
+      </c>
+      <c r="J5" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E5" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>95</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="I5" s="5">
-        <v>4</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="39.6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:10" ht="66" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>98</v>
+        <v>27</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="G6" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="I6" s="5">
         <v>5</v>
       </c>
       <c r="J6" s="6" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1436,31 +1426,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="I2" s="5">
         <v>5</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
@@ -1468,31 +1458,31 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="I3" s="5">
         <v>3</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -1511,10 +1501,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
@@ -1522,7 +1512,7 @@
         <v>16</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -1530,7 +1520,7 @@
         <v>17</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -1538,7 +1528,7 @@
         <v>18</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -1546,7 +1536,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
@@ -1554,7 +1544,7 @@
         <v>20</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
@@ -1562,7 +1552,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
@@ -1570,7 +1560,7 @@
         <v>22</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
@@ -1578,7 +1568,7 @@
         <v>23</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -1586,7 +1576,7 @@
         <v>24</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
@@ -1594,7 +1584,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>

--- a/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
+++ b/files/Group6_Template_PRJ301_AI_Usage_Report_Template.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/82a2b92dce9c2cdf/Tài liệu/GitHub/PRJ301-Nh-m-6/files/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\asus\Downloads\LABnhom6\PRJ301-Nh-m-6\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_D3A7A346085E1B9BB8E6B63E047569DD2EE5F18B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{271C5304-3FA0-4FF8-8C58-0751B1D05874}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="0.Overview" sheetId="1" r:id="rId1"/>
@@ -23,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="138">
   <si>
     <t>PRJ301 - Project AI Usage Report</t>
   </si>
@@ -335,17 +334,123 @@
   </si>
   <si>
     <t>Group6_Session1_GitDDL.png</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Testing  </t>
+  </si>
+  <si>
+    <t>Generate realistic Git commit history mock data to test free-riding detection algorithm</t>
+  </si>
+  <si>
+    <t>INSERT statements containing 30 dummy commit records across 4 team members with varying lines added/deleted.</t>
+  </si>
+  <si>
+    <t>Adjusted commit author emails to match FPT student ID formats (SE18xxxx@fpt.edu.vn) and intentionally created 1 free-rider pattern (&lt; 2 commits) for algorithm testing.</t>
+  </si>
+  <si>
+    <t>30 SQL INSERT statements, 4 mock user profiles</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Mock data had uniform commit timestamps, which required manual distribution over a 7-day period to simulate real student activity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Research</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Evaluate JGit library in Java for parsing local .git repository folders without relying on external web APIs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ChatGPT </t>
+  </si>
+  <si>
+    <t>Sample Java code using org.eclipse.jgit.api.Git to open a local repository, walk through the commit graph, and extract author statistics.</t>
+  </si>
+  <si>
+    <t>Wrapped repository file access in try-with-resources to prevent memory leaks and file lock issues on Windows.</t>
+  </si>
+  <si>
+    <t>1 Java class template (GitParserHelper.java)</t>
+  </si>
+  <si>
+    <t>Parsing large repositories locally using JGit can cause high CPU usage if commit trees are walked sequentially without caching.</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Draft Functional Use Cases &amp; SRS for "Git Analytics &amp; Free-Riding Detection" (FE-L-03) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ChatGPT</t>
+  </si>
+  <si>
+    <t>"Sync Git Repository", "Calculate Member Contribution", "Flag Free-Rider Alert", "Export Contribution Report"</t>
+  </si>
+  <si>
+    <t>Refined acceptance criteria to match AITA rubric standards, specifically adding a threshold constraint (e.g., alert triggered if contribution &lt; 10%).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4 Use Case specifications, 1 SRS section draft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SRS draft initially lacked exception handling logic for deleted or force-pushed Git commits.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UI/UX Prototype design for Student View - Personal Git Contribution &amp; Peer Comparison  </t>
+  </si>
+  <si>
+    <t>HTML/CSS snippet rendering a progress bar showing student's contribution percentage versus team average, along with commit activity timeline.</t>
+  </si>
+  <si>
+    <t>Adjusted layout styling to integrate smoothly with the overall AITA Bootstrap UI framework.</t>
+  </si>
+  <si>
+    <t>Group6_Session1_GitUseCases.</t>
+  </si>
+  <si>
+    <t>Group6_Session1_StudentGitUI</t>
+  </si>
+  <si>
+    <t>Group6_Session1_JGitResearch</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Group6_Session1_GitMockData</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1 HTML/CSS view component template</t>
+  </si>
+  <si>
+    <t>CSS progress bars were static and lacked dynamic Javascript rendering for live data binding.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Design </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Design GitCommitDAO.java and ContributionScoreDAO.java interface and method signatures</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Java interface definitions containing CRUD methods (insertCommitLog(), getContributionByGroupId(), getFreeRiderList()).</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Ensured JDBC prepared statements use parameterized queries to prevent SQL Injection when storing commit messages.</t>
+  </si>
+  <si>
+    <t>Group6_Session1_GitDAO</t>
+  </si>
+  <si>
+    <t>2 Java DAO interfaces</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Generated methods returned raw ResultSet instead of mapping directly to Data Transfer Objects (DTO/Beans).</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -518,7 +623,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Bình thường" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -817,15 +922,15 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
     <col min="2" max="5" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="28.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
@@ -834,7 +939,7 @@
       <c r="D1" s="15"/>
       <c r="E1" s="15"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -845,7 +950,7 @@
       <c r="D3" s="15"/>
       <c r="E3" s="15"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,7 +961,7 @@
       <c r="D4" s="15"/>
       <c r="E4" s="15"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -867,7 +972,7 @@
       <c r="D5" s="15"/>
       <c r="E5" s="15"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -878,7 +983,7 @@
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -887,7 +992,7 @@
       <c r="D7" s="15"/>
       <c r="E7" s="15"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>8</v>
       </c>
@@ -898,7 +1003,7 @@
       <c r="D8" s="15"/>
       <c r="E8" s="15"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>9</v>
       </c>
@@ -909,7 +1014,7 @@
       <c r="D9" s="15"/>
       <c r="E9" s="15"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>10</v>
       </c>
@@ -918,7 +1023,7 @@
       <c r="D11" s="12"/>
       <c r="E11" s="13"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>11</v>
       </c>
@@ -935,7 +1040,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>1</v>
       </c>
@@ -950,7 +1055,7 @@
       </c>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>2</v>
       </c>
@@ -965,7 +1070,7 @@
       </c>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -980,7 +1085,7 @@
       </c>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>4</v>
       </c>
@@ -995,7 +1100,7 @@
       </c>
       <c r="E16" s="2"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>5</v>
       </c>
@@ -1027,9 +1132,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1043,7 +1148,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1075,7 +1180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1107,7 +1212,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1139,7 +1244,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="52.8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" ht="52.8" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1171,7 +1276,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="5" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1203,7 +1308,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="66" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1235,67 +1340,167 @@
         <v>97</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" s="5"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="6"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="6"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" s="5"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="6"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" s="5"/>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="6"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="6"/>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" s="5"/>
-      <c r="B10" s="6"/>
-      <c r="C10" s="6"/>
-      <c r="D10" s="6"/>
-      <c r="E10" s="6"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="6"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="5"/>
-      <c r="B11" s="6"/>
-      <c r="C11" s="6"/>
-      <c r="D11" s="6"/>
-      <c r="E11" s="6"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="6"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="6"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="I7" s="5">
+        <v>5</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="5">
+        <v>4</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="I9" s="5">
+        <v>4</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="79.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="I10" s="5">
+        <v>4</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="66" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="I11" s="5">
+        <v>5</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="5"/>
       <c r="B12" s="6"/>
       <c r="C12" s="6"/>
@@ -1307,7 +1512,7 @@
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="5"/>
       <c r="B13" s="6"/>
       <c r="C13" s="6"/>
@@ -1319,7 +1524,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="5"/>
       <c r="B14" s="6"/>
       <c r="C14" s="6"/>
@@ -1331,7 +1536,7 @@
       <c r="I14" s="5"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="5"/>
       <c r="B15" s="6"/>
       <c r="C15" s="6"/>
@@ -1343,7 +1548,7 @@
       <c r="I15" s="5"/>
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="5"/>
       <c r="B16" s="6"/>
       <c r="C16" s="6"/>
@@ -1355,7 +1560,7 @@
       <c r="I16" s="5"/>
       <c r="J16" s="6"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="10"/>
       <c r="B30" s="10"/>
       <c r="C30" s="10"/>
@@ -1369,13 +1574,14 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J3"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="14" customWidth="1"/>
@@ -1389,7 +1595,7 @@
     <col min="10" max="10" width="26" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
         <v>16</v>
       </c>
@@ -1421,7 +1627,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1453,7 +1659,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1491,15 +1697,15 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
     <col min="2" max="2" width="90" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>43</v>
       </c>
@@ -1507,7 +1713,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="8" t="s">
         <v>16</v>
       </c>
@@ -1515,7 +1721,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="8" t="s">
         <v>17</v>
       </c>
@@ -1523,7 +1729,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="8" t="s">
         <v>18</v>
       </c>
@@ -1531,7 +1737,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="8" t="s">
         <v>19</v>
       </c>
@@ -1539,7 +1745,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="8" t="s">
         <v>20</v>
       </c>
@@ -1547,7 +1753,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="8" t="s">
         <v>21</v>
       </c>
@@ -1555,7 +1761,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" ht="39.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8" t="s">
         <v>22</v>
       </c>
@@ -1563,7 +1769,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="8" t="s">
         <v>23</v>
       </c>
@@ -1571,7 +1777,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="8" t="s">
         <v>24</v>
       </c>
@@ -1579,7 +1785,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A11" s="8" t="s">
         <v>25</v>
       </c>
